--- a/results/run_annee_dyn/metrics_benchmark_rc.xlsx
+++ b/results/run_annee_dyn/metrics_benchmark_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,90 @@
         <v>0.0003854785521154987</v>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>benchmark, step 15min, 1jour/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1008934822805013</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3176373439639951</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1266547807108517</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.50140837</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.002206891177884614</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9896878235134081</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.447878700204198</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1008886119118303</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3176296773159434</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0003854785521154987</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>benchmark, step 15min, 1jour/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1008934822805013</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3176373439639951</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1266547807108517</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.50140837</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.002206891177884614</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9896878235134081</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.447878700204198</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1008886119118303</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3176296773159434</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0003854785521154987</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>benchmark, step 15min, 1jour/4</t>
         </is>
